--- a/output/pdf_financials_xlsx/BUZ.P.xlsx
+++ b/output/pdf_financials_xlsx/BUZ.P.xlsx
@@ -737,10 +737,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.034502</v>
+        <v>0.110931</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.048091</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.056735</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.090432</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>0.065729</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>0.116182</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>0.042217</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>0.035533</v>
       </c>
     </row>
     <row r="11">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.034502</v>
+        <v>-0.110931</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-0.056735</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-0.090432</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>-0.065729</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>-0.116182</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>-0.042217</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>-0.035533</v>
       </c>
     </row>
     <row r="12">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
